--- a/output/graficos_dimensiones/comunal_d_env_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:17</t>
+    <t xml:space="preserve">2026-09-10 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:31</t>
+    <t xml:space="preserve">2026-09-12 22:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_aysen.xlsx
@@ -57,19 +57,19 @@
     <t xml:space="preserve">Guaitecas</t>
   </si>
   <si>
+    <t xml:space="preserve">Tortel</t>
+  </si>
+  <si>
     <t xml:space="preserve">O'Higgins</t>
   </si>
   <si>
-    <t xml:space="preserve">Tortel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:42</t>
+    <t xml:space="preserve">2026-09-24 00:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>180</v>
+        <v>196.04</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>146.26</v>
+        <v>155.42</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>135.51</v>
+        <v>145.8</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>93.84</v>
+        <v>100.9</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>84.42</v>
+        <v>91.07</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>80.22</v>
+        <v>86.65</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>75.94</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>65.73</v>
+        <v>70.81</v>
       </c>
     </row>
     <row r="10">
@@ -635,13 +635,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>11302</v>
+        <v>11303</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -652,13 +652,13 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>11303</v>
+        <v>11302</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>44.07</v>
+        <v>47.76</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:11</t>
+    <t xml:space="preserve">2026-10-02 16:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:27</t>
+    <t xml:space="preserve">2026-10-04 10:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:42</t>
+    <t xml:space="preserve">2026-10-05 16:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
